--- a/Extra Data for project/Questions files/Safety اسئلة.xlsx
+++ b/Extra Data for project/Questions files/Safety اسئلة.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20380"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ahushu01\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Company Coding Projects\Skill Matrix Questions\skill-matrix\Extra Data for project\Questions files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A4FA81E-9C10-4C8A-B29A-85BC83EC6984}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB018C75-9811-4F9E-A042-B0E031FD2E40}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="8364" xr2:uid="{52E7F6EC-7E8A-4640-8DFE-7B3CFBB2E3A8}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" activeTab="1" xr2:uid="{52E7F6EC-7E8A-4640-8DFE-7B3CFBB2E3A8}"/>
   </bookViews>
   <sheets>
     <sheet name="الأسئلة" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="107">
   <si>
     <t>القسم</t>
   </si>
@@ -313,6 +314,39 @@
   </si>
   <si>
     <t>Safty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mcq </t>
+  </si>
+  <si>
+    <t>t/f</t>
+  </si>
+  <si>
+    <t>Q_ID</t>
+  </si>
+  <si>
+    <t>Category</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Question</t>
+  </si>
+  <si>
+    <t>Opt_A</t>
+  </si>
+  <si>
+    <t>Opt_B</t>
+  </si>
+  <si>
+    <t>Opt_C</t>
+  </si>
+  <si>
+    <t>Opt_D</t>
+  </si>
+  <si>
+    <t>Answer</t>
   </si>
 </sst>
 </file>
@@ -442,7 +476,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -470,6 +504,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -789,19 +826,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D7F141D-AD7B-440E-9218-54EAB5A7B489}">
   <dimension ref="A1:I47"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19" style="5" customWidth="1"/>
-    <col min="2" max="2" width="14.5546875" style="5" customWidth="1"/>
+    <col min="2" max="2" width="14.5703125" style="5" customWidth="1"/>
     <col min="3" max="3" width="43" style="5" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14" style="9" customWidth="1"/>
-    <col min="5" max="5" width="21.77734375" style="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" style="9" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="14" style="9" customWidth="1"/>
-    <col min="8" max="8" width="6.21875" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="8.88671875" style="5"/>
+    <col min="8" max="8" width="6.28515625" style="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="8.85546875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -827,7 +864,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>95</v>
       </c>
@@ -853,7 +890,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>95</v>
       </c>
@@ -879,7 +916,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>95</v>
       </c>
@@ -905,7 +942,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>95</v>
       </c>
@@ -931,7 +968,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>95</v>
       </c>
@@ -957,7 +994,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>95</v>
       </c>
@@ -983,7 +1020,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>95</v>
       </c>
@@ -1009,7 +1046,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>95</v>
       </c>
@@ -1035,7 +1072,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>95</v>
       </c>
@@ -1061,7 +1098,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>95</v>
       </c>
@@ -1087,7 +1124,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>95</v>
       </c>
@@ -1114,7 +1151,7 @@
       </c>
       <c r="I12" s="7"/>
     </row>
-    <row r="13" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="44.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>95</v>
       </c>
@@ -1140,7 +1177,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>95</v>
       </c>
@@ -1166,7 +1203,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>95</v>
       </c>
@@ -1192,7 +1229,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>95</v>
       </c>
@@ -1218,7 +1255,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>95</v>
       </c>
@@ -1228,15 +1265,15 @@
       <c r="C17" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="10"/>
-      <c r="E17" s="10"/>
-      <c r="F17" s="10"/>
-      <c r="G17" s="10"/>
+      <c r="D17" s="11"/>
+      <c r="E17" s="11"/>
+      <c r="F17" s="11"/>
+      <c r="G17" s="11"/>
       <c r="H17" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>95</v>
       </c>
@@ -1246,15 +1283,15 @@
       <c r="C18" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="D18" s="10"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="10"/>
-      <c r="G18" s="10"/>
+      <c r="D18" s="11"/>
+      <c r="E18" s="11"/>
+      <c r="F18" s="11"/>
+      <c r="G18" s="11"/>
       <c r="H18" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>95</v>
       </c>
@@ -1264,15 +1301,15 @@
       <c r="C19" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="D19" s="10"/>
-      <c r="E19" s="10"/>
-      <c r="F19" s="10"/>
-      <c r="G19" s="10"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
+      <c r="G19" s="11"/>
       <c r="H19" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>95</v>
       </c>
@@ -1282,15 +1319,15 @@
       <c r="C20" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="D20" s="10"/>
-      <c r="E20" s="10"/>
-      <c r="F20" s="10"/>
-      <c r="G20" s="10"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="11"/>
+      <c r="G20" s="11"/>
       <c r="H20" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>95</v>
       </c>
@@ -1300,15 +1337,15 @@
       <c r="C21" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="11"/>
+      <c r="G21" s="11"/>
       <c r="H21" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>95</v>
       </c>
@@ -1318,15 +1355,15 @@
       <c r="C22" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="D22" s="10"/>
-      <c r="E22" s="10"/>
-      <c r="F22" s="10"/>
-      <c r="G22" s="10"/>
+      <c r="D22" s="11"/>
+      <c r="E22" s="11"/>
+      <c r="F22" s="11"/>
+      <c r="G22" s="11"/>
       <c r="H22" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>95</v>
       </c>
@@ -1336,15 +1373,15 @@
       <c r="C23" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="D23" s="10"/>
-      <c r="E23" s="10"/>
-      <c r="F23" s="10"/>
-      <c r="G23" s="10"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
+      <c r="F23" s="11"/>
+      <c r="G23" s="11"/>
       <c r="H23" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>95</v>
       </c>
@@ -1354,15 +1391,15 @@
       <c r="C24" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
+      <c r="D24" s="11"/>
+      <c r="E24" s="11"/>
+      <c r="F24" s="11"/>
+      <c r="G24" s="11"/>
       <c r="H24" s="5" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>95</v>
       </c>
@@ -1372,15 +1409,15 @@
       <c r="C25" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="D25" s="10"/>
-      <c r="E25" s="10"/>
-      <c r="F25" s="10"/>
-      <c r="G25" s="10"/>
+      <c r="D25" s="11"/>
+      <c r="E25" s="11"/>
+      <c r="F25" s="11"/>
+      <c r="G25" s="11"/>
       <c r="H25" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>95</v>
       </c>
@@ -1390,136 +1427,136 @@
       <c r="C26" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D26" s="10"/>
-      <c r="E26" s="10"/>
-      <c r="F26" s="10"/>
-      <c r="G26" s="10"/>
+      <c r="D26" s="11"/>
+      <c r="E26" s="11"/>
+      <c r="F26" s="11"/>
+      <c r="G26" s="11"/>
       <c r="H26" s="5" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="9"/>
       <c r="B27" s="9"/>
       <c r="C27" s="9"/>
       <c r="E27" s="8"/>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="9"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
       <c r="E28" s="8"/>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="9"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
       <c r="E29" s="8"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" s="9"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
       <c r="E30" s="8"/>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="9"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
       <c r="E31" s="8"/>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="9"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
       <c r="E32" s="8"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="9"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
       <c r="E33" s="8"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="9"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
       <c r="E34" s="8"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="9"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
       <c r="E35" s="8"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="9"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
       <c r="E36" s="8"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="8"/>
       <c r="B37" s="8"/>
       <c r="C37" s="8"/>
       <c r="D37" s="8"/>
       <c r="E37" s="8"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="9"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
       <c r="E38" s="8"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="9"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
       <c r="E39" s="8"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="9"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
       <c r="E40" s="8"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="9"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
       <c r="E41" s="8"/>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="9"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
       <c r="E42" s="8"/>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="9"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
       <c r="E43" s="8"/>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="9"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
       <c r="E44" s="8"/>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="9"/>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
       <c r="E45" s="8"/>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="9"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
       <c r="E46" s="8"/>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="9"/>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -1541,4 +1578,614 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBCB09DF-A138-47AE-8726-94EEA2556788}">
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1" t="s">
+        <v>103</v>
+      </c>
+      <c r="G1" t="s">
+        <v>104</v>
+      </c>
+      <c r="H1" t="s">
+        <v>105</v>
+      </c>
+      <c r="I1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>29</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>30</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>40</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>49</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>51</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>52</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>54</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D14" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D15" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E15" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D16" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>13</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D17" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E17" s="10"/>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10"/>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" s="10"/>
+      <c r="F18" s="10"/>
+      <c r="G18" s="10"/>
+      <c r="H18" s="10"/>
+      <c r="I18" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E19" s="10"/>
+      <c r="F19" s="10"/>
+      <c r="G19" s="10"/>
+      <c r="H19" s="10"/>
+      <c r="I19" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D20" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E20" s="10"/>
+      <c r="F20" s="10"/>
+      <c r="G20" s="10"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D21" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D22" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="10"/>
+      <c r="F22" s="10"/>
+      <c r="G22" s="10"/>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B23" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="10"/>
+      <c r="F23" s="10"/>
+      <c r="G23" s="10"/>
+      <c r="H23" s="10"/>
+      <c r="I23" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B24" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E24" s="10"/>
+      <c r="F24" s="10"/>
+      <c r="G24" s="10"/>
+      <c r="H24" s="10"/>
+      <c r="I24" s="10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B25" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D25" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="E25" s="10"/>
+      <c r="F25" s="10"/>
+      <c r="G25" s="10"/>
+      <c r="H25" s="10"/>
+      <c r="I25" s="10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B26" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" s="10"/>
+      <c r="F26" s="10"/>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10"/>
+      <c r="I26" s="10">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Extra Data for project/Questions files/Safety اسئلة.xlsx
+++ b/Extra Data for project/Questions files/Safety اسئلة.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Company Coding Projects\Skill Matrix Questions\skill-matrix\Extra Data for project\Questions files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB018C75-9811-4F9E-A042-B0E031FD2E40}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE3AAFC4-33DD-49FE-874E-30C5570D0C9C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7425" activeTab="1" xr2:uid="{52E7F6EC-7E8A-4640-8DFE-7B3CFBB2E3A8}"/>
   </bookViews>
